--- a/VerveStacks_BRA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
+++ b/VerveStacks_BRA_grids/SuppXLS/Scen_Par-AR6_R10.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_BRA_grids\SuppXLS\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8EC9858C-4A05-4C05-B843-8E6B9C025E86}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{DBB09466-1270-46CC-A6F2-E56AFAC09D3A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" firstSheet="6" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1238,10 +1238,10 @@
     <t>WaP</t>
   </si>
   <si>
-    <t>WaP,WaD,SaD,RaP,RaD,FaD,FaP,SaP</t>
+    <t>RaD,WaD,FaD,SaD,WaP,FaP,SaP,RaP</t>
   </si>
   <si>
-    <t>RaN,FaP,SaP,SaN,WaN,RaP,FaN,WaP</t>
+    <t>WaP,RaP,FaN,SaN,WaN,FaP,SaP,RaN</t>
   </si>
 </sst>
 </file>
@@ -24879,7 +24879,7 @@
 </file>
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6B67201F-7BB3-46C6-910D-C6F3954797EC}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7C41D517-5F53-4A56-8132-948127D381CF}">
   <dimension ref="A9:AN125"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -25267,7 +25267,7 @@
         <v>151</v>
       </c>
       <c r="AM14">
-        <v>0.37657499999999994</v>
+        <v>0.37657500000000005</v>
       </c>
       <c r="AN14" t="s">
         <v>379</v>
@@ -25417,7 +25417,7 @@
         <v>151</v>
       </c>
       <c r="AM17">
-        <v>0.47745833333333326</v>
+        <v>0.47745833333333332</v>
       </c>
       <c r="AN17" t="s">
         <v>379</v>
@@ -25467,7 +25467,7 @@
         <v>151</v>
       </c>
       <c r="AM18">
-        <v>0.49290833333333328</v>
+        <v>0.49290833333333334</v>
       </c>
       <c r="AN18" t="s">
         <v>379</v>
@@ -25617,7 +25617,7 @@
         <v>151</v>
       </c>
       <c r="AM21">
-        <v>0.49416666666666664</v>
+        <v>0.4941666666666667</v>
       </c>
       <c r="AN21" t="s">
         <v>379</v>
@@ -25717,7 +25717,7 @@
         <v>151</v>
       </c>
       <c r="AM23">
-        <v>0.5011916666666667</v>
+        <v>0.50119166666666659</v>
       </c>
       <c r="AN23" t="s">
         <v>379</v>
@@ -25817,7 +25817,7 @@
         <v>151</v>
       </c>
       <c r="AM25">
-        <v>0.43922500000000003</v>
+        <v>0.43922499999999998</v>
       </c>
       <c r="AN25" t="s">
         <v>379</v>
@@ -25917,7 +25917,7 @@
         <v>151</v>
       </c>
       <c r="AM27">
-        <v>0.43380000000000002</v>
+        <v>0.43379999999999996</v>
       </c>
       <c r="AN27" t="s">
         <v>379</v>
@@ -26117,7 +26117,7 @@
         <v>151</v>
       </c>
       <c r="AM31">
-        <v>0.41860000000000003</v>
+        <v>0.41859999999999992</v>
       </c>
       <c r="AN31" t="s">
         <v>379</v>
@@ -26217,7 +26217,7 @@
         <v>151</v>
       </c>
       <c r="AM33">
-        <v>0.42898333333333333</v>
+        <v>0.42898333333333344</v>
       </c>
       <c r="AN33" t="s">
         <v>379</v>
@@ -26267,7 +26267,7 @@
         <v>151</v>
       </c>
       <c r="AM34">
-        <v>0.41612500000000008</v>
+        <v>0.41612499999999991</v>
       </c>
       <c r="AN34" t="s">
         <v>379</v>
@@ -26317,7 +26317,7 @@
         <v>151</v>
       </c>
       <c r="AM35">
-        <v>0.42348333333333327</v>
+        <v>0.42348333333333338</v>
       </c>
       <c r="AN35" t="s">
         <v>379</v>
@@ -26417,7 +26417,7 @@
         <v>151</v>
       </c>
       <c r="AM37">
-        <v>0.42235000000000006</v>
+        <v>0.42235</v>
       </c>
       <c r="AN37" t="s">
         <v>379</v>
@@ -28237,7 +28237,7 @@
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4E8B9F93-6C5D-41AD-9B02-D97D93881996}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBADB078-6D53-4CAB-BA78-34EE39C67C8A}">
   <dimension ref="A9:AN1390"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -30125,7 +30125,7 @@
         <v>380</v>
       </c>
       <c r="AM35">
-        <v>0.46473333333333339</v>
+        <v>0.46473333333333328</v>
       </c>
       <c r="AN35" t="s">
         <v>379</v>
@@ -30275,7 +30275,7 @@
         <v>385</v>
       </c>
       <c r="AM38">
-        <v>0.4996666666666667</v>
+        <v>0.49966666666666665</v>
       </c>
       <c r="AN38" t="s">
         <v>379</v>
@@ -30325,7 +30325,7 @@
         <v>380</v>
       </c>
       <c r="AM39">
-        <v>0.46993333333333331</v>
+        <v>0.46993333333333337</v>
       </c>
       <c r="AN39" t="s">
         <v>379</v>
@@ -31725,7 +31725,7 @@
         <v>380</v>
       </c>
       <c r="AM67">
-        <v>0.41606666666666664</v>
+        <v>0.41606666666666675</v>
       </c>
       <c r="AN67" t="s">
         <v>379</v>
@@ -31775,7 +31775,7 @@
         <v>382</v>
       </c>
       <c r="AM68">
-        <v>0.46343333333333331</v>
+        <v>0.46343333333333336</v>
       </c>
       <c r="AN68" t="s">
         <v>379</v>
@@ -32075,7 +32075,7 @@
         <v>385</v>
       </c>
       <c r="AM74">
-        <v>0.47373333333333334</v>
+        <v>0.47373333333333328</v>
       </c>
       <c r="AN74" t="s">
         <v>379</v>
@@ -32325,7 +32325,7 @@
         <v>380</v>
       </c>
       <c r="AM79">
-        <v>0.39276666666666671</v>
+        <v>0.39276666666666665</v>
       </c>
       <c r="AN79" t="s">
         <v>379</v>
@@ -32375,7 +32375,7 @@
         <v>382</v>
       </c>
       <c r="AM80">
-        <v>0.47500000000000009</v>
+        <v>0.47500000000000003</v>
       </c>
       <c r="AN80" t="s">
         <v>379</v>
@@ -32475,7 +32475,7 @@
         <v>385</v>
       </c>
       <c r="AM82">
-        <v>0.46533333333333338</v>
+        <v>0.46533333333333332</v>
       </c>
       <c r="AN82" t="s">
         <v>379</v>
@@ -32575,7 +32575,7 @@
         <v>382</v>
       </c>
       <c r="AM84">
-        <v>0.4913333333333334</v>
+        <v>0.49133333333333334</v>
       </c>
       <c r="AN84" t="s">
         <v>379</v>
@@ -32775,7 +32775,7 @@
         <v>382</v>
       </c>
       <c r="AM88">
-        <v>0.45799999999999996</v>
+        <v>0.45800000000000002</v>
       </c>
       <c r="AN88" t="s">
         <v>379</v>
@@ -33775,7 +33775,7 @@
         <v>382</v>
       </c>
       <c r="AM108">
-        <v>0.46809999999999996</v>
+        <v>0.46810000000000002</v>
       </c>
       <c r="AN108" t="s">
         <v>379</v>
@@ -33925,7 +33925,7 @@
         <v>380</v>
       </c>
       <c r="AM111">
-        <v>0.41213333333333341</v>
+        <v>0.4121333333333333</v>
       </c>
       <c r="AN111" t="s">
         <v>379</v>
@@ -33975,7 +33975,7 @@
         <v>382</v>
       </c>
       <c r="AM112">
-        <v>0.44593333333333335</v>
+        <v>0.44593333333333329</v>
       </c>
       <c r="AN112" t="s">
         <v>379</v>
@@ -34275,7 +34275,7 @@
         <v>385</v>
       </c>
       <c r="AM118">
-        <v>0.44503333333333334</v>
+        <v>0.44503333333333339</v>
       </c>
       <c r="AN118" t="s">
         <v>379</v>
@@ -34525,7 +34525,7 @@
         <v>380</v>
       </c>
       <c r="AM123">
-        <v>0.33779999999999993</v>
+        <v>0.33780000000000004</v>
       </c>
       <c r="AN123" t="s">
         <v>379</v>
